--- a/reference-model/DomainModelSample/domain_model_setup.xlsx
+++ b/reference-model/DomainModelSample/domain_model_setup.xlsx
@@ -152,7 +152,7 @@
     <x:t>Repair the element</x:t>
   </x:si>
   <x:si>
-    <x:t>Cost = area_sqm x per-material repair rate. See TreatmentTrigger.cs.</x:t>
+    <x:t>Cost = area_sqm x the per-material repair rate. Triggered in the treatments trigger.</x:t>
   </x:si>
   <x:si>
     <x:t>replace</x:t>
@@ -161,9 +161,6 @@
     <x:t>Replace the element</x:t>
   </x:si>
   <x:si>
-    <x:t>Cost = area_sqm x per-material replacement rate. See TreatmentTrigger.cs.</x:t>
-  </x:si>
-  <x:si>
     <x:t>RMaint</x:t>
   </x:si>
   <x:si>
@@ -180,6 +177,9 @@
   </x:si>
   <x:si>
     <x:t>output_parameter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cost = area_sqm x the per-material replacement rate. Triggered in the treatments trigger.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -916,12 +916,12 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
         <x:v>45</x:v>
@@ -930,10 +930,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -955,13 +955,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="C1" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
         <x:v>12</x:v>
